--- a/assets/constructions/examples/ctd_mr3.xlsx
+++ b/assets/constructions/examples/ctd_mr3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,60 +614,81 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H3094718-10-150</t>
+          <t>71N606002MT ALTIN-MT1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WALTER</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>H3094718</t>
+          <t>71N6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MKSO</t>
-        </is>
-      </c>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>0.38</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>h9</t>
+          <t>e8</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>0.62</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -680,18 +701,18 @@
           <t>h6</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ALTIN-MT1</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>TAX</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>PWZ-NORM L</t>
-        </is>
-      </c>
+          <t>AlTiN</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
         <v>0</v>
       </c>
@@ -699,19 +720,21 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X2" t="n">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="Y2" t="n">
-        <v>150</v>
+        <v>56.68</v>
       </c>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -725,7 +748,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2017/Общий каталог WALTER 2017</t>
+          <t>2020/End Mills Widia Hanita RU</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -737,23 +760,34 @@
         <v>0</v>
       </c>
       <c r="AK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
         <v>1</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6771 3.000</t>
+          <t>EFF-S4-08 035/26C08R1.3M IC903</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GUHRING</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>EFF-S</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -763,30 +797,30 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>h10</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>1.62</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
       <c r="J3" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7</v>
+      </c>
       <c r="M3" t="n">
         <v>4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-8</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -794,27 +828,19 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>IC903</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Signum</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Werksnorm</t>
-        </is>
-      </c>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
         <v>0</v>
       </c>
@@ -822,23 +848,19 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -852,7 +874,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2020 www.guhring.com</t>
+          <t>2019/rotation-toos-2019-milling-tools.pdf</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -865,51 +887,68 @@
       </c>
       <c r="AK3" t="b">
         <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EFF-S4-16 055/42C16R2.6M IC903</t>
+          <t>MD025-16.0A6B200C-WJ30RA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EFF-S</t>
+          <t>MD025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMKSH</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>h9</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>7</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -921,19 +960,27 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>IC903</t>
+          <t>WJ30RA</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>TiAlN + TiAl</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>PWZ-NORM L</t>
+        </is>
+      </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
@@ -950,7 +997,9 @@
         <v>92</v>
       </c>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>15.2</v>
+      </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
         <v>42</v>
@@ -967,7 +1016,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2019/rotation-toos-2019-milling-tools.pdf</t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -979,23 +1028,34 @@
         <v>0</v>
       </c>
       <c r="AK4" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>MNS</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MD025-08.0A5B100C-WJ30RA</t>
+          <t>70NS06002 ALTIN-MT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WALTER</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD025</t>
+          <t>70NS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1005,36 +1065,36 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>h9</t>
+          <t>e8</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>0.67</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>0.32</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1049,20 +1109,16 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>WJ30RA</t>
+          <t>ALTIN-MT</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>TiAlN + TiAl</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>PWZ-NORM L</t>
-        </is>
-      </c>
+          <t>AlTiN</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
         <v>0</v>
       </c>
@@ -1070,21 +1126,21 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X5" t="n">
         <v>63</v>
       </c>
       <c r="Y5" t="n">
-        <v>63</v>
+        <v>62.68</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>25</v>
+        <v>17.75</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1098,7 +1154,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2017/Общий каталог WALTER 2017</t>
+          <t>2020/End Mills Widia Hanita RU</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1110,54 +1166,73 @@
         <v>0</v>
       </c>
       <c r="AK5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
         <v>1</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>PMS</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R215.H4-20050EAC06H 1610</t>
+          <t>MD025-12.0A6B150C-WJ30RA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CoroMill® Plura R215.Hx..AC..H</t>
+          <t>MD025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>h9</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>45</v>
+        <v>0.8</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1167,27 +1242,23 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>h8</t>
+          <t>h6</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1610</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>HC</t>
-        </is>
-      </c>
+          <t>WJ30RA</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PVD TIALN </t>
+          <t>TiAlN + TiAl</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>COROMANT</t>
+          <t>PWZ-NORM L</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1197,37 +1268,35 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="X6" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="Y6" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>11.4</v>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>HA</t>
         </is>
       </c>
-      <c r="AE6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.449</v>
-      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 07.2 </t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1239,7 +1308,18 @@
         <v>0</v>
       </c>
       <c r="AK6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>MNS</t>
+        </is>
       </c>
     </row>
   </sheetData>
